--- a/tame_output/ON/bt/strategyON_20240909.xlsx
+++ b/tame_output/ON/bt/strategyON_20240909.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>138.9%</t>
         </is>
       </c>
     </row>
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.3%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.6%</t>
+          <t>-661.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.5%</t>
+          <t>-125.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.4%</t>
+          <t>588.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-151.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2080"/>
+  <dimension ref="A1:G2081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.63481327712577</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
@@ -49401,6 +49401,29 @@
       </c>
       <c r="G2080" t="n">
         <v>4.919098120905979</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="2" t="n">
+        <v>45543</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>3.645382918715256</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>4.505084966071336</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>-4.995376290084084</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>2.506578025723955</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>0.7233222018686857</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>4.939078287192547</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240909.xlsx
+++ b/tame_output/ON/bt/strategyON_20240909.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-52.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>124.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.1%</t>
+          <t>-677.4%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.6%</t>
+          <t>-146.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.5%</t>
+          <t>588.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.7%</t>
+          <t>-152.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2081"/>
+  <dimension ref="A1:G2082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>2.932720855873487</v>
       </c>
       <c r="D1904" t="n">
         <v>-7.085932548115547</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3211295702889383</v>
+        <v>0.09799141231352015</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6023869095472272</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.794426868120569</v>
+        <v>2.571288710145151</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>2.833981641880641</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.953657074484661</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2753005457484474</v>
+        <v>0.05216238777302928</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4701114359163405</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.775052938306255</v>
+        <v>2.551914780330837</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>2.836796702568278</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.797918741924919</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.1172727814845631</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.314373103356599</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.871310998529737</v>
+        <v>2.648172840554319</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>2.849703043791937</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.712954075195599</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.1641649893999495</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2294084366272794</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.935196139790988</v>
+        <v>2.712057981815569</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>2.721727114192718</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.818544064968703</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>-0.006046936108510703</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3349984264003837</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.743866216327906</v>
+        <v>2.520728058352488</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>2.770271456069804</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.750309480343276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.06979123961874656</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3165831035278477</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803459751928514</v>
+        <v>2.580321593953096</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.653650647431397</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.602369438935677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.01234644754337921</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2962621876192902</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.699031492835242</v>
+        <v>2.475893334859824</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.644936661177919</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.549399916681688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.02482027019149635</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2432926653653013</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.722099219934157</v>
+        <v>2.498961061958739</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.637976049082826</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.383611720721397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.08417493648051977</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2432926653653013</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.715138607839064</v>
+        <v>2.492000449863645</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.652438403463969</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.350248514242629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.1119825734531701</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2432926653653013</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.729600962220207</v>
+        <v>2.506462804244789</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.646970523923164</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.241989377120107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.1498183487613738</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2432926653653013</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.724133082679402</v>
+        <v>2.500994924703984</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.644468617933741</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.118698242302976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.1966328966988029</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1200015305481708</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.795605857580257</v>
+        <v>2.572467699604839</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.652169596171066</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.066001375171685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.225412621788645</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.06730466341687963</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.834924956096357</v>
+        <v>2.611786798120939</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.647950304518117</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.822235933188241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.3186995069290735</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.06730466341687963</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.830705664443407</v>
+        <v>2.607567506467989</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.650074618438133</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.732460260811768</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.3567340897996782</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.005705218502569609</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.86978964531201</v>
+        <v>2.646651487336591</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.642816693421835</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.482609866862694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.4494163223630103</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.005705218502569609</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.862531720295712</v>
+        <v>2.639393562320294</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.646415816942484</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.306717774395262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.5233722828706315</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.005705218502569609</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.86613084381636</v>
+        <v>2.642992685840942</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.659743322997037</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.135271311372798</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.605278374134171</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1657412445198935</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.982326227684392</v>
+        <v>2.759188069708974</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.658763800613334</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.055249024263677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.6363077665941161</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2457635316290145</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.029360077566162</v>
+        <v>2.806221919590743</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.663458601667652</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.991613282029743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.6664568645420073</v>
       </c>
       <c r="F1923" t="n">
         <v>0.309399273862949</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.072236323960839</v>
+        <v>2.849098165985421</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.644652860451447</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.897915963813348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.685130050612361</v>
       </c>
       <c r="F1924" t="n">
         <v>0.309399273862949</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.053430582744635</v>
+        <v>2.830292424769217</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.646395937076325</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.908418586878637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.6826720780111226</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2988966507976601</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>2.825733927554921</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.650325250911145</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.795932326209762</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9547340540889109</v>
+        <v>0.7315958961134927</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>2.829663241389741</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879963</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.651003834828485</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.778218639331897</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9624981127573971</v>
+        <v>0.7393599547819789</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>2.832250622645231</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.648001906048478</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.654744368018878</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.008885892502598</v>
+        <v>0.7857477345271797</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>2.829248693865225</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.649580943059092</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.434723569981868</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.098473248728016</v>
+        <v>0.8753350907525981</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>2.915559637916627</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.665475125860916</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.30185588091859</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.16751450715515</v>
+        <v>0.9443763491797323</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>2.93145382071845</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.666620970301218</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.181682797554092</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.216729584941252</v>
+        <v>0.9935914269658337</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.004703515177451</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.676709072862657</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.046429436224114</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.280919032034683</v>
+        <v>1.057780874059264</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.095943634536878</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.662746564264083</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.106304263581807</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.243006592493031</v>
+        <v>1.019868434517613</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.046056229523688</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.678035733498292</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.986484032670969</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.306223854091575</v>
+        <v>1.083085696116157</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.061345398757897</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.585679932820733</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.988953739132775</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.212880170829294</v>
+        <v>0.9897420128538759</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>2.967507774203255</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.504941794306035</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.057323925456785</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.104793957784992</v>
+        <v>0.8816557998095735</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>2.892335055110285</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.495378502937926</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.169196205082936</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.050481754566423</v>
+        <v>0.8273435965910045</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>2.882771763742176</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.855547497605547</v>
+        <v>2.632409339630128</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.224716280975525</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.165304560901589</v>
+        <v>0.9421664029261709</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.019802600434379</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.860114729597334</v>
+        <v>2.636976571621916</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.049242021183057</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.240061496810364</v>
+        <v>1.016923338834946</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.024369832426166</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.835856758358541</v>
+        <v>2.612718600383123</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.041317646598142</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.218973275405537</v>
+        <v>0.995835117430119</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.000111861187373</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.764395071759991</v>
+        <v>2.541256913784573</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.035039444028294</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.150022869834927</v>
+        <v>0.9268847118595085</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>2.932417096130733</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.774567458192124</v>
+        <v>2.551429300216705</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.97518682482457</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.184136303948548</v>
+        <v>0.96099814597313</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>2.942589482562865</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.769513728765984</v>
+        <v>2.546375570790566</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.888943361798193</v>
+        <v>-3.869682683122345</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.21357995973296</v>
+        <v>0.9981460732278804</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>2.937535753136725</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.761289504210509</v>
+        <v>2.538151346235091</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.934250181197172</v>
+        <v>-3.914989502521325</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.187233007417893</v>
+        <v>0.9717991209128138</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>2.904825430775713</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.761841377243611</v>
+        <v>2.538703219268193</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.963283285899474</v>
+        <v>-3.944022607223627</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.176171638570074</v>
+        <v>0.9607377520649949</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>2.905377303808814</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.691114069134977</v>
+        <v>2.467975911159558</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.870472804448615</v>
+        <v>-3.851212125772768</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.142568523041783</v>
+        <v>0.9271346365367041</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>2.890336284570695</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.692987545059577</v>
+        <v>2.469849387084159</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.914862273778042</v>
+        <v>-3.895601595102195</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.126686211234613</v>
+        <v>0.9112523247295341</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>2.865576078897639</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.6880632535713</v>
+        <v>2.464925095595882</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.031403878883385</v>
+        <v>-4.012143200207538</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.075145277704199</v>
+        <v>0.8597113911991201</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>2.790726824346157</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.693554549401968</v>
+        <v>2.47041639142655</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.071327973465957</v>
+        <v>-4.05206729479011</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.064666935701838</v>
+        <v>0.8492330491967583</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>2.796218120176824</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.705051751170507</v>
+        <v>2.481913593195089</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.09910837136731</v>
+        <v>-4.079847692691462</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.065051978309836</v>
+        <v>0.8496180918047564</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>2.791047083204551</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.54340747117116</v>
+        <v>2.320269313195742</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.217489044097448</v>
+        <v>-4.198228365421601</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8560554292184337</v>
+        <v>0.6406215427133544</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.589072091914619</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.663557131890366</v>
+        <v>2.440418973914948</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.326103122540779</v>
+        <v>-4.306842443864932</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9327594585603067</v>
+        <v>0.7173255720552274</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.709221752633824</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.678070157992689</v>
+        <v>2.454932000017271</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.290694084292636</v>
+        <v>-4.271433405616789</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9614360999618869</v>
+        <v>0.7460022134568076</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.723734778736147</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.675489599335057</v>
+        <v>2.452351441359639</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.252310421734485</v>
+        <v>-4.233049743058638</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9742090063275159</v>
+        <v>0.7587751198224368</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.744184417613407</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.672218628180359</v>
+        <v>2.449080470204941</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.075194091699319</v>
+        <v>-4.055933413023472</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.041784567186884</v>
+        <v>0.8263506806818051</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.740913446458709</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.672902019942272</v>
+        <v>2.449763861966854</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.120286336532865</v>
+        <v>-4.101025657857018</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.024431061015379</v>
+        <v>0.8089971745103</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.704459212318988</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.666688995248687</v>
+        <v>2.443550837273269</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.940910915294097</v>
+        <v>-3.92165023661825</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.089968204817301</v>
+        <v>0.8745343183122214</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>2.792312242527834</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.647496450580276</v>
+        <v>2.424358292604858</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.985925128814703</v>
+        <v>-3.966664450138856</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.052769974740648</v>
+        <v>0.8373360882355687</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.754910360670661</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.653188012919222</v>
+        <v>2.430049854943804</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.252929639087139</v>
+        <v>-4.233668960411292</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9516597329706196</v>
+        <v>0.7362258464655402</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.643984100183837</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.652391934815724</v>
+        <v>2.429253776840306</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.354127420524311</v>
+        <v>-4.334866741848464</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9103845422922519</v>
+        <v>0.6949506557871725</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.602142733953147</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.64999189637004</v>
+        <v>2.426853738394622</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.347616453909999</v>
+        <v>-4.328355775234152</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9105888904922936</v>
+        <v>0.6951550039872143</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.599742695507464</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.646516615578285</v>
+        <v>2.423378457602867</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.328578326202702</v>
+        <v>-4.309317647526854</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9147288607834574</v>
+        <v>0.6992949742783781</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.561357247916992</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.765811017212476</v>
+        <v>2.542672859237058</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.381094128477522</v>
+        <v>-4.361833449801675</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.01301694150772</v>
+        <v>0.7975830550026404</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.680651649551182</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.766644346198609</v>
+        <v>2.543506188223191</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.39496088981144</v>
+        <v>-4.375700211135593</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.008303565960286</v>
+        <v>0.7928696794552068</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.658770228497022</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.772652876595535</v>
+        <v>2.549514718620117</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.354477897889095</v>
+        <v>-4.335217219213248</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.03050529312615</v>
+        <v>0.8150714066210707</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.664778758893948</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.670603097872735</v>
+        <v>2.447464939897317</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.206734927654092</v>
+        <v>-4.187474248978245</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9875527024973505</v>
+        <v>0.7721188159922712</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.663413394512077</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.673396719404216</v>
+        <v>2.450258561428797</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.290556148928791</v>
+        <v>-4.271295470252944</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9568178355189521</v>
+        <v>0.7413839490138727</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.666207016043558</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.450920909820456</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.284403442876006</v>
+        <v>-4.265142764200159</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9599412663317242</v>
+        <v>0.7445073798266448</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.670560988066887</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.450001386560566</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.301212741026508</v>
+        <v>-4.281952062350661</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9522980238116336</v>
+        <v>0.7368641373065543</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.659555885916697</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.516336940357387</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.238914742250386</v>
+        <v>-4.219654063574539</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.043552777118903</v>
+        <v>0.8281188906138242</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.753067998278182</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.318628942071514</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.037124544585228</v>
+        <v>-4.017863865909381</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9265608578990938</v>
+        <v>0.7111269713940145</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.674170915293802</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.388919174393689</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.088011257271423</v>
+        <v>-4.068750578595576</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.976496405146791</v>
+        <v>0.7610625186417117</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.713929120004261</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.403546910509733</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.001400514621615</v>
+        <v>-3.982139835945768</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.025768438322758</v>
+        <v>0.8103345518176783</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.7757322948434</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.402082891334405</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.0616098126269</v>
+        <v>-4.042349133951053</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.000220699945316</v>
+        <v>0.7847868134402363</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.7381426968649</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.400574509374333</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.012423163942548</v>
+        <v>-3.993162485266701</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.018386977458985</v>
+        <v>0.8029530909539053</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.736634314904829</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.400437376809769</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.96805003230398</v>
+        <v>-3.948789353628133</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.035999097549848</v>
+        <v>0.820565211044769</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.763121061323406</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.39483117094836</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.990530383162865</v>
+        <v>-3.971269704487018</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.021400751344885</v>
+        <v>0.8059668648398055</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.757514855461997</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.401212927976164</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.942874652601809</v>
+        <v>-3.923613973925962</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.046844800597112</v>
+        <v>0.8314109140920325</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>2.792490050826435</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.406105301350889</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.842356494103054</v>
+        <v>-3.823095815427207</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.091944437371339</v>
+        <v>0.8765105508662592</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>2.857693319300413</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.392859973826762</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.826451164670702</v>
+        <v>-3.807190485994854</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.085061241620152</v>
+        <v>0.8696273551150724</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>2.796980395350741</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.39695767643739</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.781612763062304</v>
+        <v>-3.762352084386456</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.10709430487414</v>
+        <v>0.8916604183690602</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>2.803804157728292</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.401118616068468</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.801111219304312</v>
+        <v>-3.781850540628465</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.103455862008414</v>
+        <v>0.8880219755033349</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.779114312591427</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.406998218596305</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.756908382218411</v>
+        <v>-3.737647703542564</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.127016599370612</v>
+        <v>0.9115827128655323</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>2.811515617370804</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.405408219065553</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.764468048055458</v>
+        <v>-3.745207369379611</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.12240273350504</v>
+        <v>0.9069688469999611</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>2.842807660245944</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.456655984248592</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.606176630516186</v>
+        <v>-3.586915951840339</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.236967065703789</v>
+        <v>1.02153317919871</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>2.894055425428983</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.455096688842846</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.39853462688171</v>
+        <v>-3.379273948205863</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.318464571751833</v>
+        <v>1.103030685246753</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.017081332203922</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.450044917081116</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.347502534159182</v>
+        <v>-3.328241855483335</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.333825637079114</v>
+        <v>1.118391750574034</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.042648816075709</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.467232321173821</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.282278353031976</v>
+        <v>-3.263017674356129</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.377102713622701</v>
+        <v>1.161668827117622</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.098970728844737</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.463193293473101</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.244851332960842</v>
+        <v>-3.225590654284995</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.388034493950435</v>
+        <v>1.172600607445356</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.098082623961526</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.464450085804341</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.26496298899555</v>
+        <v>-3.245702310319703</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.381246623867792</v>
+        <v>1.165812737362713</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.105955823291218</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.625007856825552</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.236549725895667</v>
+        <v>-3.21728904721982</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.553169700128956</v>
+        <v>1.337735813623877</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.231128256664572</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.745120766043369</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.161767464870654</v>
+        <v>-3.142506786194807</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.703195513756778</v>
+        <v>1.487761627251699</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.396110522497397</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.736828742057228</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.135683380606846</v>
+        <v>-3.116422701930999</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.705337123476161</v>
+        <v>1.489903236971081</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.387818498511256</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.735021937641008</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.047805467497726</v>
+        <v>-3.028544788821879</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.738681484303588</v>
+        <v>1.523247597798509</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.455567079549045</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959861</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.752576343367799</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.038913006104442</v>
+        <v>-3.019652327428595</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.759792874587693</v>
+        <v>1.544358988082614</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.473121485275837</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945369</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.744431390772383</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.20738912307432</v>
+        <v>-3.188128444398473</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.684257475204326</v>
+        <v>1.468823588699246</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.448207831250472</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782713</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.725701087960245</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.76113293044488</v>
+        <v>-2.741872251769033</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.844029649443964</v>
+        <v>1.628595762938884</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.372646326636555</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.78467134563264</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.716365110457149</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.738411826761728</v>
+        <v>-2.719151148085881</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.843782113414129</v>
+        <v>1.62834822690905</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.363310349133459</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>2.875271236308318</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.86761364005577</v>
+        <v>-2.848352961379923</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.951007513947681</v>
+        <v>1.735573627442602</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.444695387008203</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644416</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>2.912349058801965</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.893488038529796</v>
+        <v>-2.874227359853949</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.977735577051718</v>
+        <v>1.762301690546638</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.508720174728894</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>2.90902441479151</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.886433348314622</v>
+        <v>-2.867172669638775</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.977232809127332</v>
+        <v>1.761798922622253</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.509628344847544</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.76667349633112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>2.919030568436252</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.859482123988134</v>
+        <v>-2.840221445312287</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.998019452502669</v>
+        <v>1.78258556599759</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.528562706108917</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.103133700581211</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.881026351818921</v>
+        <v>-2.861765673143074</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.173504893515314</v>
+        <v>1.958071007010235</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.712665838253876</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.095250395484205</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.903434469623793</v>
+        <v>-2.884173790947946</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.156658341296358</v>
+        <v>1.941224454791278</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.70478253315687</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155036</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.097304395033842</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.931658705201394</v>
+        <v>-2.912398026525547</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.147422646614955</v>
+        <v>1.931988760109876</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.717622584177292</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.153558112755689</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.941099631089924</v>
+        <v>-2.921838952414077</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.199899993981391</v>
+        <v>1.984466107476311</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>3.847332572425174</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.15644920730099</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.029976262258398</v>
+        <v>-3.010715583582551</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.167240436059302</v>
+        <v>1.951806549554223</v>
       </c>
       <c r="F2007" t="n">
         <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.020035846244808</v>
+        <v>3.796897688269391</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.154561020194765</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.106306239859304</v>
+        <v>-3.087045561183456</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.134820257912715</v>
+        <v>1.919386371407636</v>
       </c>
       <c r="F2008" t="n">
         <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.018147659138584</v>
+        <v>3.795009501163166</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.149381249797627</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.199970184536845</v>
+        <v>-3.180709505860998</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.092174909644561</v>
+        <v>1.876741023139481</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.733631363959503</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.14781526000778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.3615386100641</v>
+        <v>-3.342277931388253</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.025981549643811</v>
+        <v>1.810547663138731</v>
       </c>
       <c r="F2010" t="n">
         <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.655995619890928</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.160888666873698</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.469839271934219</v>
+        <v>-3.450578593258372</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.995734691761681</v>
+        <v>1.780300805256602</v>
       </c>
       <c r="F2011" t="n">
         <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.669069026756846</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378396</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.152893863656638</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.487643243654964</v>
+        <v>-3.468382564979116</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.980618299856324</v>
+        <v>1.765184413351244</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7764326435667122</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.841891607772084</v>
+        <v>3.618753449796666</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006979</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.15141790478364</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.515544030764437</v>
+        <v>-3.496283352088589</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.967982026139537</v>
+        <v>1.752548139634457</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7418357194237774</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.819657494413325</v>
+        <v>3.596519336437907</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787391</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.148182348760839</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.63807013346733</v>
+        <v>-3.618809454791483</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.915736029035578</v>
+        <v>1.700302142530498</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6193096167208835</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.742906276768788</v>
+        <v>3.519768118793369</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585942</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.214888308351343</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.868584629652919</v>
+        <v>-3.849323950977072</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.890236190151846</v>
+        <v>1.674802303646767</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3887951205352947</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.671303538647938</v>
+        <v>3.44816538067252</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.35520002735319</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.217329714877363</v>
+        <v>-4.198069036201516</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.891049875063916</v>
+        <v>1.675615988558836</v>
       </c>
       <c r="F2016" t="n">
         <v>0.2800471666163969</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.746366485298446</v>
+        <v>3.523228327323028</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237099</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.42418029649883</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.371316132653503</v>
+        <v>-4.352055453977656</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.898435577099099</v>
+        <v>1.68300169059402</v>
       </c>
       <c r="F2017" t="n">
         <v>0.2800471666163969</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.815346754444086</v>
+        <v>3.592208596468668</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.410231498618951</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.320794228825838</v>
+        <v>-4.301533550149991</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.904695540750286</v>
+        <v>1.689261654245207</v>
       </c>
       <c r="F2018" t="n">
         <v>0.2800471666163969</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.801397956564207</v>
+        <v>3.578259798588789</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.422101987674365</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.573269382833562</v>
+        <v>-4.554008704157715</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.815575968202611</v>
+        <v>1.600142081697531</v>
       </c>
       <c r="F2019" t="n">
         <v>0.2800471666163969</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.813268445619621</v>
+        <v>3.590130287644203</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973162</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.423312522193308</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.866165139312974</v>
+        <v>-4.846904460637127</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.69962820012979</v>
+        <v>1.48419431362471</v>
       </c>
       <c r="F2020" t="n">
         <v>0.2800471666163969</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.814478980138565</v>
+        <v>3.591340822163147</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.42743426442063</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.052829267447782</v>
+        <v>-5.033568588771935</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.629084291103188</v>
+        <v>1.413650404598108</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2533081957918371</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.802557339871151</v>
+        <v>3.579419181895732</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.422512117156819</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.198849954361744</v>
+        <v>-5.179589275685897</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.565753869073792</v>
+        <v>1.350319982568713</v>
       </c>
       <c r="F2022" t="n">
         <v>0.2442251039979801</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.792185337531026</v>
+        <v>3.569047179555608</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.584716173855863</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.29056396347133</v>
+        <v>-5.271303284795483</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.691272322129002</v>
+        <v>1.475838435623923</v>
       </c>
       <c r="F2023" t="n">
         <v>0.2442251039979801</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.95438939423007</v>
+        <v>3.731251236254652</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.579562811819677</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.322215622531299</v>
+        <v>-5.302954943855452</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.673458296468829</v>
+        <v>1.458024409963749</v>
       </c>
       <c r="F2024" t="n">
         <v>0.2390566467535399</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.94613495784722</v>
+        <v>3.722996799871801</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.589792229388169</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.404150440800183</v>
+        <v>-5.384889762124335</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.650913786729766</v>
+        <v>1.435479900224687</v>
       </c>
       <c r="F2025" t="n">
         <v>0.2291219011664597</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.950403528063463</v>
+        <v>3.727265370088045</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.598717867844071</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.50612656304859</v>
+        <v>-5.486865884372743</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.619048976286306</v>
+        <v>1.403615089781227</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1271457789180521</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.898143493170321</v>
+        <v>3.675005335194903</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.590870755088246</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.396120279571369</v>
+        <v>-5.376859600895521</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.65520437692137</v>
+        <v>1.43977049041629</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1503503508353273</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.904219123564861</v>
+        <v>3.681080965589443</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818525</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.595120765810221</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.253060703830442</v>
+        <v>-5.233800025154595</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.716678217939715</v>
+        <v>1.501244331434635</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1583637774253066</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.913277190240823</v>
+        <v>3.690139032265405</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.602381648692757</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.951613978358605</v>
+        <v>-4.932353299682758</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.844517791010986</v>
+        <v>1.629083904505906</v>
       </c>
       <c r="F2029" t="n">
         <v>0.4598105028971439</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.101406108406461</v>
+        <v>3.878267950431043</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.603352826445467</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.976204222593789</v>
+        <v>-4.956943543917942</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.835652871069623</v>
+        <v>1.620218984564543</v>
       </c>
       <c r="F2030" t="n">
         <v>0.4598105028971439</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.102377286159172</v>
+        <v>3.879239128183754</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.604195730825223</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.925165846587269</v>
+        <v>-4.905905167911421</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.856911125851986</v>
+        <v>1.641477239346907</v>
       </c>
       <c r="F2031" t="n">
         <v>0.4598105028971439</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.103220190538927</v>
+        <v>3.880082032563509</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.623233829699368</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.884026551720638</v>
+        <v>-4.86476587304479</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.892404942672784</v>
+        <v>1.676971056167705</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5009497977637747</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.146941866333052</v>
+        <v>3.923803708357633</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.439417825823303</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.787391639701998</v>
+        <v>-4.76813096102615</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.747242903604175</v>
+        <v>1.531809017099095</v>
       </c>
       <c r="F2033" t="n">
         <v>0.5975847097824146</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.02110680966817</v>
+        <v>3.797968651692752</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.442919869897267</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.91797237423284</v>
+        <v>-4.898711695556993</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.698512653865802</v>
+        <v>1.483078767360722</v>
       </c>
       <c r="F2034" t="n">
         <v>0.4670039752515721</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.946260413023628</v>
+        <v>3.723122255048211</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.427346688973349</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.753476040041878</v>
+        <v>-4.734215361366031</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.748738006618269</v>
+        <v>1.53330412011319</v>
       </c>
       <c r="F2035" t="n">
         <v>0.631500309442534</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.029385032614289</v>
+        <v>3.80624687463887</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.426534399409779</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.676377438500006</v>
+        <v>-4.657116759824159</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.778765157671448</v>
+        <v>1.563331271166368</v>
       </c>
       <c r="F2036" t="n">
         <v>0.631500309442534</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.028572743050718</v>
+        <v>3.8054345850753</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.436403178534852</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.686762633389895</v>
+        <v>-4.667501954714048</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.784479858840565</v>
+        <v>1.569045972335485</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6211151145526447</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.032210405241857</v>
+        <v>3.809072247266439</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.507240184311277</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.70535079211212</v>
+        <v>-4.686090113436273</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.8478816011281</v>
+        <v>1.63244771462302</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6025269558304194</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.091894515784947</v>
+        <v>3.868756357809529</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.504109195129575</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.705649338808156</v>
+        <v>-4.686388660132309</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.844631193267984</v>
+        <v>1.629197306762904</v>
       </c>
       <c r="F2039" t="n">
         <v>0.6022284091343835</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.088584398585624</v>
+        <v>3.865446240610205</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.508640090068967</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.604826205117728</v>
+        <v>-4.585565526441881</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.889491341683546</v>
+        <v>1.674057455178467</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6146926246187373</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.100593822815627</v>
+        <v>3.877455664840209</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.50876934354751</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.414044844365321</v>
+        <v>-4.394784165689474</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.965933139463052</v>
+        <v>1.750499252957973</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8054739853711447</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.215191892745615</v>
+        <v>3.992053734770197</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.488606189285107</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.3070814865159</v>
+        <v>-4.287820807840053</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.988555328340418</v>
+        <v>1.773121441835338</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8639385933309461</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.230107503259092</v>
+        <v>4.006969345283674</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.523573125897165</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.251750898614137</v>
+        <v>-4.23249021993829</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.045654500113181</v>
+        <v>1.830220613608102</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9192691812327083</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.298272792612209</v>
+        <v>4.07513463463679</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.517259693798603</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.239696771701174</v>
+        <v>-4.220436093025327</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.044162718779804</v>
+        <v>1.828728832274725</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9313233081456711</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.299191836661424</v>
+        <v>4.076053678686006</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.519140323982739</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.280851891269395</v>
+        <v>-4.261591212593548</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.029581301136651</v>
+        <v>1.814147414631572</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8901681885774502</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.276379395104627</v>
+        <v>4.053241237129209</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.531991349860621</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.212803328577865</v>
+        <v>-4.193542649902018</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.069651752091146</v>
+        <v>1.854217865586066</v>
       </c>
       <c r="F2046" t="n">
         <v>0.95821675126898</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.330059558597427</v>
+        <v>4.106921400622009</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.552194020034215</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.444403721747366</v>
+        <v>-4.425143043071519</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.99721426499694</v>
+        <v>1.78178037849186</v>
       </c>
       <c r="F2047" t="n">
         <v>0.95821675126898</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.350262228771022</v>
+        <v>4.127124070795603</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498973</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.535800256101097</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.494455267276585</v>
+        <v>-4.475194588600738</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.960799882852134</v>
+        <v>1.745365996347055</v>
       </c>
       <c r="F2048" t="n">
         <v>0.95821675126898</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.333868464837904</v>
+        <v>4.110730306862486</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800102</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.496052169694564</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.66956209985303</v>
+        <v>-4.650301421177183</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.851009063415023</v>
+        <v>1.635575176909944</v>
       </c>
       <c r="F2049" t="n">
         <v>0.95821675126898</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.29412037843137</v>
+        <v>4.070982220455952</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660854</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.503074788691504</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.638276079312575</v>
+        <v>-4.619015400636727</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.870546090628145</v>
+        <v>1.655112204123066</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9895027718094354</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.319914609752583</v>
+        <v>4.096776451777165</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395091</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.602245788264408</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.48525068719929</v>
+        <v>-4.465990008523443</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.030927247046363</v>
+        <v>1.815493360541284</v>
       </c>
       <c r="F2051" t="n">
         <v>1.142528163922719</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.510900844593459</v>
+        <v>4.28776268661804</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.789712013172701</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.51355800107256</v>
+        <v>-4.494297322396713</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.207070546405347</v>
+        <v>1.991636659900268</v>
       </c>
       <c r="F2052" t="n">
         <v>1.142528163922719</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.698367069501751</v>
+        <v>4.475228911526333</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.759114964526784</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.680151226186083</v>
+        <v>-4.660890547510236</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.109836207714021</v>
+        <v>1.894402321208942</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9759349388091969</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.567814085787719</v>
+        <v>4.344675927812302</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.762791367188501</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.657115432824517</v>
+        <v>-4.63785475414867</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.122726927720365</v>
+        <v>1.907293041215286</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9759349388091969</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.571490488449437</v>
+        <v>4.34835233047402</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.760409422311997</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.62786945236882</v>
+        <v>-4.608608773692973</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.132043375026139</v>
+        <v>1.91660948852106</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9759349388091969</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.569108543572932</v>
+        <v>4.345970385597515</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.757702661469632</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.734795000246671</v>
+        <v>-4.715534321570824</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.086566395032634</v>
+        <v>1.871132508527555</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8690093909313455</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.502246454003857</v>
+        <v>4.279108296028439</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.759131463612866</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.87981355875392</v>
+        <v>-4.860552880078073</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.029987773772969</v>
+        <v>1.814553887267889</v>
       </c>
       <c r="F2057" t="n">
         <v>0.723990832424097</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.416664121042742</v>
+        <v>4.193525963067325</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.859062702870619</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.998155324538637</v>
+        <v>-4.97889464586279</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.082582306716835</v>
+        <v>1.867148420211755</v>
       </c>
       <c r="F2058" t="n">
         <v>0.7346768709869871</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.523006983438229</v>
+        <v>4.299868825462811</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.856848399996558</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.049565746859345</v>
+        <v>-5.030305068183498</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.05980383491449</v>
+        <v>1.844369948409411</v>
       </c>
       <c r="F2059" t="n">
         <v>0.7346768709869871</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.520792680564168</v>
+        <v>4.297654522588751</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.856751528070847</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.128985198067097</v>
+        <v>-5.10972451939125</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.027939182505679</v>
+        <v>1.8125052960006</v>
       </c>
       <c r="F2060" t="n">
         <v>0.7346768709869871</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.520695808638457</v>
+        <v>4.297557650663039</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.85674542162889</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.224448195984315</v>
+        <v>-5.205187517308468</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.989747876896835</v>
+        <v>1.774313990391756</v>
       </c>
       <c r="F2061" t="n">
         <v>0.7346768709869871</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.520689702196501</v>
+        <v>4.297551544221083</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.854841818191501</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.1600722851336</v>
+        <v>-5.140811606457753</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.013594637799732</v>
+        <v>1.798160751294652</v>
       </c>
       <c r="F2062" t="n">
         <v>0.7990527818377022</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.55741164526954</v>
+        <v>4.334273487294122</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.860575635939227</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.215441447265794</v>
+        <v>-5.196180768589946</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.997180790694581</v>
+        <v>1.781746904189502</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7990527818377022</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.563145463017267</v>
+        <v>4.340007305041849</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.86011399928216</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.260879227096621</v>
+        <v>-5.241618548420774</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.978544042105182</v>
+        <v>1.763110155600103</v>
       </c>
       <c r="F2064" t="n">
         <v>0.7562077911595426</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.536976831953304</v>
+        <v>4.313838673977886</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.879988392132478</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.172672392949043</v>
+        <v>-5.153411714273195</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.033701168614532</v>
+        <v>1.818267282109453</v>
       </c>
       <c r="F2065" t="n">
         <v>0.7562077911595426</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.556851224803623</v>
+        <v>4.333713066828205</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.863689092657206</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.066637397743733</v>
+        <v>-5.047376719067886</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.059815867221384</v>
+        <v>1.844381980716304</v>
       </c>
       <c r="F2066" t="n">
         <v>0.7562077911595426</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.540551925328351</v>
+        <v>4.317413767352932</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307673</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.866120042121252</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.883425734610638</v>
+        <v>-4.864165055934791</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.135531481938667</v>
+        <v>1.920097595433589</v>
       </c>
       <c r="F2067" t="n">
         <v>0.7562077911595426</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.542982874792396</v>
+        <v>4.319844716816978</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.831911227969142</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.811704287596787</v>
+        <v>-4.79244360892094</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.130011246592098</v>
+        <v>1.914577360087019</v>
       </c>
       <c r="F2068" t="n">
         <v>0.8279292381733933</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.551806928848595</v>
+        <v>4.328668770873178</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.778826973890314</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.789331261989081</v>
+        <v>-4.770070583313234</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.085876202756351</v>
+        <v>1.870442316251273</v>
       </c>
       <c r="F2069" t="n">
         <v>0.8391849892862948</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.505476125437508</v>
+        <v>4.282337967462091</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>3.964025178775669</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.822347557899826</v>
+        <v>-4.803086879223978</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.257867889277409</v>
+        <v>2.042434002772331</v>
       </c>
       <c r="F2070" t="n">
         <v>0.7697476126195433</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.649011904322813</v>
+        <v>4.425873746347396</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>3.955946404603918</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.810819922250217</v>
+        <v>-4.79155924357437</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.254400169365502</v>
+        <v>2.038966282860423</v>
       </c>
       <c r="F2071" t="n">
         <v>0.8287482708209057</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.676333525071879</v>
+        <v>4.453195367096462</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>3.959614517125707</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.908161423592586</v>
+        <v>-4.888900744916739</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.219131681350342</v>
+        <v>2.003697794845264</v>
       </c>
       <c r="F2072" t="n">
         <v>0.7843280886554174</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.653349528294375</v>
+        <v>4.430211370318958</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427685</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>3.960865599318545</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.994017452932552</v>
+        <v>-4.974756774256705</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.186040351807194</v>
+        <v>1.970606465302116</v>
       </c>
       <c r="F2073" t="n">
         <v>0.7419520194292824</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.629174968951532</v>
+        <v>4.406036810976115</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>3.943284801139047</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.002854250348672</v>
+        <v>-4.983593571672825</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.164924834661248</v>
+        <v>1.94949094815617</v>
       </c>
       <c r="F2074" t="n">
         <v>0.7345098467879316</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.607128867187224</v>
+        <v>4.383990709211806</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>3.953449312184096</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.09423681291413</v>
+        <v>-5.074976134238283</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.138536320680114</v>
+        <v>1.923102434175036</v>
       </c>
       <c r="F2075" t="n">
         <v>0.6431272842224733</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.562463840692998</v>
+        <v>4.339325682717581</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.055577570008364</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.082530094927124</v>
+        <v>-5.063269416251277</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.245347265699185</v>
+        <v>2.029913379194106</v>
       </c>
       <c r="F2076" t="n">
         <v>0.6548340022094797</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.67161612930947</v>
+        <v>4.448477971334052</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.058609908739768</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.982866590843462</v>
+        <v>-4.963605912167615</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.288245006064055</v>
+        <v>2.072811119558975</v>
       </c>
       <c r="F2077" t="n">
         <v>0.7180210854131662</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.712560717963086</v>
+        <v>4.489422559987668</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.271514742017827</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.993182689009814</v>
+        <v>-4.973922010333967</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.497023400075572</v>
+        <v>2.281589513570493</v>
       </c>
       <c r="F2078" t="n">
         <v>0.7180210854131662</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.925465551241144</v>
+        <v>4.702327393265726</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.270693408929916</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.993088720992441</v>
+        <v>-4.973828042316594</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.496239654194611</v>
+        <v>2.280805767689531</v>
       </c>
       <c r="F2079" t="n">
         <v>0.7183909467604842</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.924866134961625</v>
+        <v>4.701727976986207</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63481327712577</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.26492539487427</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.000307545192285</v>
+        <v>-4.981046866516438</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.487584110459027</v>
+        <v>2.272150223953948</v>
       </c>
       <c r="F2080" t="n">
         <v>0.7183909467604842</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.919098120905979</v>
+        <v>4.69595996293056</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,45 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.645382918715256</v>
+        <v>3.647907242740925</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.505084966071336</v>
+        <v>4.26492539487427</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.995376290084084</v>
+        <v>-4.9800984433984</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.506578025723955</v>
+        <v>2.272529593201163</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.7233222018686857</v>
+        <v>0.7183909467604842</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.939078287192547</v>
+        <v>4.69595996293056</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="2" t="n">
+        <v>45544</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>3.887298152656555</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>4.359411497323526</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>-5.158006192402877</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>2.295852596048628</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0.7183909467604842</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>4.790446065379816</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240909.xlsx
+++ b/tame_output/ON/bt/strategyON_20240909.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-52.3%</t>
+          <t>-54.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>105.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>421.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-677.4%</t>
+          <t>-676.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-146.6%</t>
+          <t>-165.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.6%</t>
+          <t>145.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-306.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-155.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705543</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>2.932720855873487</v>
+        <v>2.913571079510888</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.085932548115547</v>
+        <v>-7.064306127509174</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.09799141231352015</v>
+        <v>0.08749220419347115</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6023869095472272</v>
+        <v>-0.6224184780616828</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.571288710145151</v>
+        <v>2.540119992673879</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>2.833981641880641</v>
+        <v>2.814831865518043</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.953657074484661</v>
+        <v>-6.932030653878288</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.05216238777302928</v>
+        <v>0.04166317965298028</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4701114359163405</v>
+        <v>-0.4901430044307962</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.551914780330837</v>
+        <v>2.520746062859565</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.836796702568278</v>
+        <v>2.81764692620568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.776292321318546</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1172727814845631</v>
+        <v>0.1067735733645141</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.314373103356599</v>
+        <v>-0.3344046718710546</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.648172840554319</v>
+        <v>2.617004123083047</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>2.849703043791937</v>
+        <v>2.830553267429338</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.691327654589227</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1641649893999495</v>
+        <v>0.1536657812799005</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2294084366272794</v>
+        <v>-0.249440005141735</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.712057981815569</v>
+        <v>2.680889264344298</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.721727114192718</v>
+        <v>2.702577337830119</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.796917644362331</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.006046936108510703</v>
+        <v>-0.0165461442285606</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3349984264003837</v>
+        <v>-0.3550299949148394</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.520728058352488</v>
+        <v>2.489559340881216</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.770271456069804</v>
+        <v>2.751121679707206</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.728683059736904</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06979123961874656</v>
+        <v>0.05929203149869666</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3165831035278477</v>
+        <v>-0.3366146720423034</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.580321593953096</v>
+        <v>2.549152876481824</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.653650647431397</v>
+        <v>2.634500871068798</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.580743018329304</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01234644754337921</v>
+        <v>0.001847239423329317</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2962621876192902</v>
+        <v>-0.3162937561337458</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.475893334859824</v>
+        <v>2.444724617388551</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.644936661177919</v>
+        <v>2.62578688481532</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.527773496075316</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02482027019149635</v>
+        <v>0.01432106207144646</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.263324233879757</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.498961061958739</v>
+        <v>2.467792344487466</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.637976049082826</v>
+        <v>2.618826272720227</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.361985300115025</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.08417493648051977</v>
+        <v>0.07367572836046987</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.263324233879757</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.492000449863645</v>
+        <v>2.460831732392373</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.652438403463969</v>
+        <v>2.63328862710137</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.328622093636256</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1119825734531701</v>
+        <v>0.1014833653331202</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.263324233879757</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.506462804244789</v>
+        <v>2.475294086773516</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.646970523923164</v>
+        <v>2.627820747560565</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.220362956513735</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1498183487613738</v>
+        <v>0.1393191406413239</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.263324233879757</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.500994924703984</v>
+        <v>2.469826207232711</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.644468617933741</v>
+        <v>2.625318841571142</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-6.097071821696604</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1966328966988029</v>
+        <v>0.1861336885787535</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1200015305481708</v>
+        <v>-0.1400330990626265</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.572467699604839</v>
+        <v>2.541298982133567</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.652169596171066</v>
+        <v>2.633019819808467</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-6.044374954565312</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.225412621788645</v>
+        <v>0.2149134136685951</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08733623193133527</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.611786798120939</v>
+        <v>2.580618080649666</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.647950304518117</v>
+        <v>2.628800528155518</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.800609512581868</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3186995069290735</v>
+        <v>0.3082002988090236</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08733623193133527</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.607567506467989</v>
+        <v>2.576398788996717</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.650074618438133</v>
+        <v>2.630924842075534</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.710833840205396</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3567340897996782</v>
+        <v>0.3462348816796283</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02573678701702525</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.646651487336591</v>
+        <v>2.615482769865319</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.642816693421835</v>
+        <v>2.623666917059236</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.460983446256321</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4494163223630103</v>
+        <v>0.4389171142429604</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02573678701702525</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.639393562320294</v>
+        <v>2.608224844849021</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.646415816942484</v>
+        <v>2.627266040579885</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.285091353788889</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5233722828706315</v>
+        <v>0.5128730747505821</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02573678701702525</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.642992685840942</v>
+        <v>2.61182396836967</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.659743322997037</v>
+        <v>2.640593546634439</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.113644890766426</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.605278374134171</v>
+        <v>0.5947791660141211</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1657412445198935</v>
+        <v>0.1457096760054379</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.759188069708974</v>
+        <v>2.728019352237701</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.658763800613334</v>
+        <v>2.639614024250736</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-5.033622603657305</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6363077665941161</v>
+        <v>0.6258085584740662</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2457635316290145</v>
+        <v>0.2257319631145588</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.806221919590743</v>
+        <v>2.775053202119471</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.663458601667652</v>
+        <v>2.644308825305053</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-4.96998686142337</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6664568645420073</v>
+        <v>0.6559576564219574</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2893677053484934</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.849098165985421</v>
+        <v>2.817929448514149</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.644652860451447</v>
+        <v>2.625503084088848</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.876289543206975</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.685130050612361</v>
+        <v>0.6746308424923111</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2893677053484934</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.830292424769217</v>
+        <v>2.799123707297945</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.646395937076325</v>
+        <v>2.627246160713726</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.886792166272264</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6826720780111226</v>
+        <v>0.6721728698910729</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2788650822832045</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.825733927554921</v>
+        <v>2.794565210083649</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.650325250911145</v>
+        <v>2.631175474548546</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.795932326209762</v>
+        <v>-4.77430590560339</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7315958961134927</v>
+        <v>0.7210966879934428</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2788650822832045</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.829663241389741</v>
+        <v>2.798494523918469</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879963</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.651003834828485</v>
+        <v>2.631854058465886</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.778218639331897</v>
+        <v>-4.756592218725524</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7393599547819789</v>
+        <v>0.728860746661929</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2820464111801213</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.832250622645231</v>
+        <v>2.801081905173959</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.648001906048478</v>
+        <v>2.62885212968588</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.654744368018878</v>
+        <v>-4.633117947412506</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7857477345271797</v>
+        <v>0.7752485264071298</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2820464111801213</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.829248693865225</v>
+        <v>2.798079976393953</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.649580943059092</v>
+        <v>2.630431166696494</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.434723569981868</v>
+        <v>-4.413097149375496</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8753350907525981</v>
+        <v>0.8648358826325482</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4232662562481015</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.915559637916627</v>
+        <v>2.884390920445355</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.665475125860916</v>
+        <v>2.646325349498317</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.30185588091859</v>
+        <v>-4.280229460312218</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9443763491797323</v>
+        <v>0.9338771410596824</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4232662562481015</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.93145382071845</v>
+        <v>2.900285103247178</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.666620970301218</v>
+        <v>2.647471193938619</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.181682797554092</v>
+        <v>-4.160056376947719</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9935914269658337</v>
+        <v>0.9830922188457838</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5434393396126005</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.004703515177451</v>
+        <v>2.973534797706179</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.676709072862657</v>
+        <v>2.657559296500059</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.046429436224114</v>
+        <v>-4.024803015617742</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.057780874059264</v>
+        <v>1.047281665939215</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6786927009425776</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.095943634536878</v>
+        <v>3.064774917065606</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.662746564264083</v>
+        <v>2.643596787901485</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.106304263581807</v>
+        <v>-4.084677842975434</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.019868434517613</v>
+        <v>1.009369226397564</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6188178735848855</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.046056229523688</v>
+        <v>3.014887512052416</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.678035733498292</v>
+        <v>2.658885957135693</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.986484032670969</v>
+        <v>-3.964857612064597</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.083085696116157</v>
+        <v>1.072586487996107</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6188178735848855</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.061345398757897</v>
+        <v>3.030176681286624</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.585679932820733</v>
+        <v>2.566530156458135</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.988953739132775</v>
+        <v>-3.967327318526403</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9897420128538759</v>
+        <v>0.9792428047338262</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.6163481671230793</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.967507774203255</v>
+        <v>2.936339056731982</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.504941794306035</v>
+        <v>2.485792017943436</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.057323925456785</v>
+        <v>-4.035697504850413</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.8816557998095735</v>
+        <v>0.8711565916895236</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6256238661592942</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.892335055110285</v>
+        <v>2.861166337639013</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.495378502937926</v>
+        <v>2.476228726575327</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.169196205082936</v>
+        <v>-4.147569784476564</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8273435965910045</v>
+        <v>0.8168443884709546</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6256238661592942</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.882771763742176</v>
+        <v>2.851603046270904</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.632409339630128</v>
+        <v>2.61325956326753</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.224716280975525</v>
+        <v>-4.203089860369153</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9421664029261709</v>
+        <v>0.9316671948061213</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6256238661592942</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.019802600434379</v>
+        <v>2.988633882963106</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.636976571621916</v>
+        <v>2.617826795259317</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.049242021183057</v>
+        <v>-4.027615600576684</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.016923338834946</v>
+        <v>1.006424130714896</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6256238661592942</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.024369832426166</v>
+        <v>2.993201114954894</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.612718600383123</v>
+        <v>2.593568824020525</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.041317646598142</v>
+        <v>-4.01969122599177</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.995835117430119</v>
+        <v>0.9853359093100693</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6256238661592942</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.000111861187373</v>
+        <v>2.968943143716102</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.541256913784573</v>
+        <v>2.522107137421974</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.035039444028294</v>
+        <v>-4.013413023421921</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9268847118595085</v>
+        <v>0.9163855037394586</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6319020687291432</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.932417096130733</v>
+        <v>2.901248378659461</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.551429300216705</v>
+        <v>2.532279523854107</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.97518682482457</v>
+        <v>-3.953560404218198</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.96099814597313</v>
+        <v>0.9504989378530802</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6319020687291432</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.942589482562865</v>
+        <v>2.911420765091593</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.546375570790566</v>
+        <v>2.527225794427967</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.869682683122345</v>
+        <v>-3.86731694119182</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9981460732278804</v>
+        <v>0.9799425936374917</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6319020687291432</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.937535753136725</v>
+        <v>2.906367035665453</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.538151346235091</v>
+        <v>2.519001569872493</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.914989502521325</v>
+        <v>-3.9126237605908</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9717991209128138</v>
+        <v>0.9535956413224254</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5910919057199124</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.904825430775713</v>
+        <v>2.87365671330444</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.538703219268193</v>
+        <v>2.519553442905594</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.944022607223627</v>
+        <v>-3.941656865293102</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9607377520649949</v>
+        <v>0.9425342724746062</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5910919057199124</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.905377303808814</v>
+        <v>2.874208586337542</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.467975911159558</v>
+        <v>2.44882613479696</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.851212125772768</v>
+        <v>-3.848846383842242</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9271346365367041</v>
+        <v>0.9089311569463154</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6839023871707718</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.890336284570695</v>
+        <v>2.859167567099423</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.469849387084159</v>
+        <v>2.450699610721561</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.895601595102195</v>
+        <v>-3.89323585317167</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9112523247295341</v>
+        <v>0.8930488451391454</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.6395129178413441</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.865576078897639</v>
+        <v>2.834407361426367</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.464925095595882</v>
+        <v>2.445775319233284</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.012143200207538</v>
+        <v>-4.009777458277012</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8597113911991201</v>
+        <v>0.8415079116087314</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5229713127360014</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.790726824346157</v>
+        <v>2.759558106874885</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.47041639142655</v>
+        <v>2.451266615063951</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.05206729479011</v>
+        <v>-4.049701552859585</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8492330491967583</v>
+        <v>0.8310295696063696</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5229713127360014</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.796218120176824</v>
+        <v>2.765049402705552</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.481913593195089</v>
+        <v>2.46276381683249</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.079847692691462</v>
+        <v>-4.077481950760937</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8496180918047564</v>
+        <v>0.8314146122143677</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.4951909148346483</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.791047083204551</v>
+        <v>2.759878365733279</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.320269313195742</v>
+        <v>2.301119536833143</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.198228365421601</v>
+        <v>-4.195862623491076</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6406215427133544</v>
+        <v>0.6224180631229657</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4279730626836721</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.589072091914619</v>
+        <v>2.557903374443347</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.440418973914948</v>
+        <v>2.421269197552349</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.306842443864932</v>
+        <v>-4.304476701934407</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7173255720552274</v>
+        <v>0.6991220924648389</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4279730626836721</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.709221752633824</v>
+        <v>2.678053035162552</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.454932000017271</v>
+        <v>2.435782223654672</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.271433405616789</v>
+        <v>-4.269067663686264</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7460022134568076</v>
+        <v>0.7277987338664189</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4279730626836721</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.723734778736147</v>
+        <v>2.692566061264875</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.452351441359639</v>
+        <v>2.43320166499704</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.233049743058638</v>
+        <v>-4.230684001128113</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7587751198224368</v>
+        <v>0.7405716402320481</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4663567252418233</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.744184417613407</v>
+        <v>2.713015700142135</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.449080470204941</v>
+        <v>2.429930693842342</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.055933413023472</v>
+        <v>-4.053567671092947</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8263506806818051</v>
+        <v>0.8081472010914164</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4663567252418233</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.740913446458709</v>
+        <v>2.709744728987437</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.449763861966854</v>
+        <v>2.430614085604256</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.101025657857018</v>
+        <v>-4.098659915926492</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8089971745103</v>
+        <v>0.7907936949199112</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.4044606820724335</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.704459212318988</v>
+        <v>2.673290494847716</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.443550837273269</v>
+        <v>2.42440106091067</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.92165023661825</v>
+        <v>-3.919284494687725</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8745343183122214</v>
+        <v>0.8563308387218327</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.5612374402431521</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.792312242527834</v>
+        <v>2.761143525056561</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.424358292604858</v>
+        <v>2.40520851624226</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.966664450138856</v>
+        <v>-3.964298708208331</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8373360882355687</v>
+        <v>0.81913260864518</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.5308885449285475</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.754910360670661</v>
+        <v>2.723741643199388</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.430049854943804</v>
+        <v>2.410900078581205</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.233668960411292</v>
+        <v>-4.231303218480766</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7362258464655402</v>
+        <v>0.7180223668751515</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.336525506885599</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.643984100183837</v>
+        <v>2.612815382712565</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.429253776840306</v>
+        <v>2.410104000477707</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.334866741848464</v>
+        <v>-4.332500999917939</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6949506557871725</v>
+        <v>0.6767471761967838</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2681166933402798</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.602142733953147</v>
+        <v>2.570974016481875</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.426853738394622</v>
+        <v>2.317676803004789</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.328355775234152</v>
+        <v>-4.325990033303627</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6951550039872143</v>
+        <v>0.5869243653695915</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2681166933402798</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.599742695507464</v>
+        <v>2.478546819008958</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.423378457602867</v>
+        <v>2.314201522213034</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.309317647526854</v>
+        <v>-4.306951905596329</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6992949742783781</v>
+        <v>0.5910643356607554</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2099330820090852</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.561357247916992</v>
+        <v>2.440161371418486</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.542672859237058</v>
+        <v>2.433495923847225</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.361833449801675</v>
+        <v>-4.35946770787115</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7975830550026404</v>
+        <v>0.6893524163850175</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2099330820090852</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.680651649551182</v>
+        <v>2.559455773052676</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.543506188223191</v>
+        <v>2.434329252833358</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.375700211135593</v>
+        <v>-4.373334469205068</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7928696794552068</v>
+        <v>0.684639040837584</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1720751652752623</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.658770228497022</v>
+        <v>2.537574351998516</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.549514718620117</v>
+        <v>2.440337783230284</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.335217219213248</v>
+        <v>-4.332851477282722</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8150714066210707</v>
+        <v>0.7068407680034479</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1720751652752623</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.664778758893948</v>
+        <v>2.543582882395442</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.447464939897317</v>
+        <v>2.338288004507484</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.187474248978245</v>
+        <v>-4.18510850704772</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7721188159922712</v>
+        <v>0.6638881773746483</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3398825225101454</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.663413394512077</v>
+        <v>2.542217518013571</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.450258561428797</v>
+        <v>2.341081626038965</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.271295470252944</v>
+        <v>-4.268929728322418</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7413839490138727</v>
+        <v>0.6331533103962501</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3398825225101454</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.666207016043558</v>
+        <v>2.545011139545052</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.450920909820456</v>
+        <v>2.341743974430623</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.265142764200159</v>
+        <v>-4.262777022269634</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7445073798266448</v>
+        <v>0.6362767412090222</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.3460352285629297</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.670560988066887</v>
+        <v>2.549365111568381</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.450001386560566</v>
+        <v>2.340824451170733</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.281952062350661</v>
+        <v>-4.279586320420136</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7368641373065543</v>
+        <v>0.6286334986889317</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.3292259304124281</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.659555885916697</v>
+        <v>2.53836000941819</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.516336940357387</v>
+        <v>2.407160004967554</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.219654063574539</v>
+        <v>-4.217288321644014</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8281188906138242</v>
+        <v>0.7198882519962013</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.3745201946868701</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.753067998278182</v>
+        <v>2.631872121779677</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.318628942071514</v>
+        <v>2.209452006681681</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.017863865909381</v>
+        <v>-4.015498123978856</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7111269713940145</v>
+        <v>0.6028963327763917</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.5725383868560245</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.674170915293802</v>
+        <v>2.552975038795296</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.388919174393689</v>
+        <v>2.279742239003856</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.068750578595576</v>
+        <v>-4.06638483666505</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7610625186417117</v>
+        <v>0.6528318800240891</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.52165167416983</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.713929120004261</v>
+        <v>2.592733243505755</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.403546910509733</v>
+        <v>2.2943699751199</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.982139835945768</v>
+        <v>-3.979774094015243</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8103345518176783</v>
+        <v>0.7021039132000555</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.6002774053749883</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.7757322948434</v>
+        <v>2.654536418344893</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.402082891334405</v>
+        <v>2.292905955944572</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.042349133951053</v>
+        <v>-4.039983392020527</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7847868134402363</v>
+        <v>0.6765561748226134</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5400681073697038</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.7381426968649</v>
+        <v>2.616946820366394</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.400574509374333</v>
+        <v>2.2913975739845</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.993162485266701</v>
+        <v>-3.990796743336176</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8029530909539053</v>
+        <v>0.6947224523362825</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5400681073697038</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.736634314904829</v>
+        <v>2.615438438406323</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.400437376809769</v>
+        <v>2.291260441419936</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.948789353628133</v>
+        <v>-3.946423611697607</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.820565211044769</v>
+        <v>0.7123345724271462</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5844412390082724</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.763121061323406</v>
+        <v>2.6419251848249</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.39483117094836</v>
+        <v>2.285654235558527</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.971269704487018</v>
+        <v>-3.968903962556492</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8059668648398055</v>
+        <v>0.6977362262221827</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5844412390082724</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.757514855461997</v>
+        <v>2.636318978963491</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.401212927976164</v>
+        <v>2.292035992586332</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.923613973925962</v>
+        <v>-3.921248231995436</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8314109140920325</v>
+        <v>0.7231802754744097</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.632096969569328</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.792490050826435</v>
+        <v>2.671294174327929</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.406105301350889</v>
+        <v>2.296928365961056</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.823095815427207</v>
+        <v>-3.820730073496682</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8765105508662592</v>
+        <v>0.7682799122486363</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.7326151280680826</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.857693319300413</v>
+        <v>2.736497442801906</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.392859973826762</v>
+        <v>2.283683038436929</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.807190485994854</v>
+        <v>-3.804824744064329</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8696273551150724</v>
+        <v>0.7613967164974498</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.6535024673588437</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796980395350741</v>
+        <v>2.675784518852235</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.39695767643739</v>
+        <v>2.287780741047557</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.762352084386456</v>
+        <v>-3.759986342455931</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8916604183690602</v>
+        <v>0.7834297797514376</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.6580459003037131</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.803804157728292</v>
+        <v>2.682608281229785</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.401118616068468</v>
+        <v>2.291941680678635</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.781850540628465</v>
+        <v>-3.779484798697939</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8880219755033349</v>
+        <v>0.7797913368857121</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.6099612590238088</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.779114312591427</v>
+        <v>2.657918436092921</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.406998218596305</v>
+        <v>2.297821283206472</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.737647703542564</v>
+        <v>-3.735281961612039</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9115827128655323</v>
+        <v>0.8033520742479094</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.6541640961097093</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.811515617370804</v>
+        <v>2.690319740872298</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.405408219065553</v>
+        <v>2.29623128367572</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.745207369379611</v>
+        <v>-3.742841627449086</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9069688469999611</v>
+        <v>0.7987382083823382</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7089675001195286</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.842807660245944</v>
+        <v>2.721611783747437</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.456655984248592</v>
+        <v>2.34747904885876</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.586915951840339</v>
+        <v>-3.584550209909814</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.02153317919871</v>
+        <v>0.9133025405810868</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7089675001195286</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.894055425428983</v>
+        <v>2.772859548930477</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.455096688842846</v>
+        <v>2.345919753453013</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.379273948205863</v>
+        <v>-3.376908206275337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.103030685246753</v>
+        <v>0.9948000466291305</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.9166095037540047</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.017081332203922</v>
+        <v>2.895885455705416</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.450044917081116</v>
+        <v>2.340867981691283</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.328241855483335</v>
+        <v>-3.325876113552809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.118391750574034</v>
+        <v>1.010161111956412</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.9676415964765327</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.042648816075709</v>
+        <v>2.921452939577203</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.467232321173821</v>
+        <v>2.358055385783988</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.263017674356129</v>
+        <v>-3.260651932425604</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.161668827117622</v>
+        <v>1.053438188499999</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.032865777603738</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.098970728844737</v>
+        <v>2.977774852346231</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.463193293473101</v>
+        <v>2.354016358083268</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.225590654284995</v>
+        <v>-3.22322491235447</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.172600607445356</v>
+        <v>1.064369968827733</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.03811731563292</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.098082623961526</v>
+        <v>2.97688674746302</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.464450085804341</v>
+        <v>2.355273150414508</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.245702310319703</v>
+        <v>-3.243336568389178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.165812737362713</v>
+        <v>1.05758209874509</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.049144660630339</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.105955823291218</v>
+        <v>2.984759946792712</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636289</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.625007856825552</v>
+        <v>2.515830921435719</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.21728904721982</v>
+        <v>-3.214923305289294</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.337735813623877</v>
+        <v>1.229505175006254</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>0.9901690978839104</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.231128256664572</v>
+        <v>3.109932380166065</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957628</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.745120766043369</v>
+        <v>2.635943830653536</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.142506786194807</v>
+        <v>-3.140141044264282</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.487761627251699</v>
+        <v>1.379530988634076</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.064951358908923</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.396110522497397</v>
+        <v>3.27491464599889</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.736828742057228</v>
+        <v>2.627651806667395</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.116422701930999</v>
+        <v>-3.114056960000474</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.489903236971081</v>
+        <v>1.381672598353458</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.064951358908923</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.387818498511256</v>
+        <v>3.266622622012749</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.735021937641008</v>
+        <v>2.625845002251175</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.028544788821879</v>
+        <v>-3.026179046891353</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.523247597798509</v>
+        <v>1.415016959180886</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.180877001332274</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.455567079549045</v>
+        <v>3.334371203050539</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959861</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.752576343367799</v>
+        <v>2.643399407977966</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.019652327428595</v>
+        <v>-3.01728658549807</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.544358988082614</v>
+        <v>1.436128349464991</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.180877001332274</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.473121485275837</v>
+        <v>3.351925608777331</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945369</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.744431390772383</v>
+        <v>2.63525445538255</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.188128444398473</v>
+        <v>-3.185762702467948</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.468823588699246</v>
+        <v>1.360592950081624</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.152929165615693</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.448207831250472</v>
+        <v>3.327011954751966</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782713</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.725701087960245</v>
+        <v>2.616524152570412</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.741872251769033</v>
+        <v>-2.739506509838508</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.628595762938884</v>
+        <v>1.520365124321261</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.058210495946061</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.372646326636555</v>
+        <v>3.251450450138048</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563264</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.716365110457149</v>
+        <v>2.607188175067316</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.719151148085881</v>
+        <v>-2.716785406155355</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.62834822690905</v>
+        <v>1.520117588291427</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.058210495946061</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.363310349133459</v>
+        <v>3.242114472634953</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.875271236308318</v>
+        <v>2.766094300918486</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.848352961379923</v>
+        <v>-2.845987219449398</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.735573627442602</v>
+        <v>1.627342988824979</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.9290086826520183</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.444695387008203</v>
+        <v>3.323499510509697</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644416</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.912349058801965</v>
+        <v>2.803172123412132</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.874227359853949</v>
+        <v>-2.871861617923424</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.762301690546638</v>
+        <v>1.654071051929015</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>0.9739202913637595</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.508720174728894</v>
+        <v>3.387524298230388</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.90902441479151</v>
+        <v>2.799847479401677</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.867172669638775</v>
+        <v>-2.86480692770825</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.761798922622253</v>
+        <v>1.65356828400463</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9809749815789333</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.509628344847544</v>
+        <v>3.388432468349038</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633112</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.919030568436252</v>
+        <v>2.809853633046419</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.840221445312287</v>
+        <v>-2.837855703381762</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.78258556599759</v>
+        <v>1.674354927379967</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9958553276066524</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.528562706108917</v>
+        <v>3.40736682961041</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.103133700581211</v>
+        <v>2.993956765191379</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.861765673143074</v>
+        <v>-2.859399931212549</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.958071007010235</v>
+        <v>1.849840368392612</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9958553276066524</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.712665838253876</v>
+        <v>3.59146996175537</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.095250395484205</v>
+        <v>2.986073460094372</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.884173790947946</v>
+        <v>-2.881808049017421</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.941224454791278</v>
+        <v>1.832993816173656</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9958553276066524</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.70478253315687</v>
+        <v>3.583586656658364</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155036</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.097304395033842</v>
+        <v>2.988127459644009</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.912398026525547</v>
+        <v>-2.910032284595022</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.931988760109876</v>
+        <v>1.823758121492253</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.013832080057961</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.717622584177292</v>
+        <v>3.596426707678786</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.153558112755689</v>
+        <v>3.044381177365856</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.921838952414077</v>
+        <v>-2.919473210483551</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.984466107476311</v>
+        <v>1.876235468858688</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.136259197601353</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.847332572425174</v>
+        <v>3.726136695926668</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.15644920730099</v>
+        <v>3.047272271911157</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.010715583582551</v>
+        <v>-3.008349841652025</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.951806549554223</v>
+        <v>1.8435759109366</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.067414134947334</v>
+        <v>1.047382566432879</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.796897688269391</v>
+        <v>3.675701811770884</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.154561020194765</v>
+        <v>3.045384084804932</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.087045561183456</v>
+        <v>-3.084679819252931</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.919386371407636</v>
+        <v>1.811155732790013</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.067414134947334</v>
+        <v>1.047382566432879</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.795009501163166</v>
+        <v>3.67381362466466</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.149381249797627</v>
+        <v>3.040204314407795</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.180709505860998</v>
+        <v>-3.178343763930473</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.876741023139481</v>
+        <v>1.768510384521858</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>0.9537186217553372</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.733631363959503</v>
+        <v>3.612435487460997</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.14781526000778</v>
+        <v>3.038638324617947</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.342277931388253</v>
+        <v>-3.339912189457728</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.810547663138731</v>
+        <v>1.702317024521109</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8269356979574578</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.655995619890928</v>
+        <v>3.534799743392422</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.160888666873698</v>
+        <v>3.051711731483866</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.450578593258372</v>
+        <v>-3.448212851327847</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.780300805256602</v>
+        <v>1.672070166638979</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8269356979574578</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.669069026756846</v>
+        <v>3.54787315025834</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378396</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.152893863656638</v>
+        <v>3.043716928266806</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.468382564979116</v>
+        <v>-3.466016823048591</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.765184413351244</v>
+        <v>1.656953774733622</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7764326435667122</v>
+        <v>0.7564010750522567</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.618753449796666</v>
+        <v>3.49755757329816</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006979</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.15141790478364</v>
+        <v>3.042240969393808</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.496283352088589</v>
+        <v>-3.493917610158064</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.752548139634457</v>
+        <v>1.644317501016834</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7418357194237774</v>
+        <v>0.7218041509093219</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.596519336437907</v>
+        <v>3.475323459939401</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787391</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.148182348760839</v>
+        <v>3.039005413371006</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.618809454791483</v>
+        <v>-3.616443712860958</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.700302142530498</v>
+        <v>1.592071503912876</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6193096167208835</v>
+        <v>0.599278048206428</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.519768118793369</v>
+        <v>3.398572242294863</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585942</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.214888308351343</v>
+        <v>3.10571137296151</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.849323950977072</v>
+        <v>-3.846958209046547</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.674802303646767</v>
+        <v>1.566571665029144</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3887951205352947</v>
+        <v>0.3687635520208393</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.44816538067252</v>
+        <v>3.326969504174014</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.35520002735319</v>
+        <v>3.246023091963357</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.198069036201516</v>
+        <v>-4.195703294270991</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.675615988558836</v>
+        <v>1.567385349941214</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.2600155981019415</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.523228327323028</v>
+        <v>3.402032450824522</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237099</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.42418029649883</v>
+        <v>3.315003361108997</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.352055453977656</v>
+        <v>-4.349689712047131</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.68300169059402</v>
+        <v>1.574771051976397</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.2600155981019415</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.592208596468668</v>
+        <v>3.471012719970162</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.410231498618951</v>
+        <v>3.301054563229118</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.301533550149991</v>
+        <v>-4.299167808219465</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.689261654245207</v>
+        <v>1.581031015627584</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.2600155981019415</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.578259798588789</v>
+        <v>3.457063922090283</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.422101987674365</v>
+        <v>3.312925052284532</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.554008704157715</v>
+        <v>-4.55164296222719</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.600142081697531</v>
+        <v>1.491911443079909</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.2600155981019415</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.590130287644203</v>
+        <v>3.468934411145697</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973162</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.423312522193308</v>
+        <v>3.314135586803475</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.846904460637127</v>
+        <v>-4.844538718706602</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.48419431362471</v>
+        <v>1.375963675007087</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.2600155981019415</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.591340822163147</v>
+        <v>3.470144945664641</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.42743426442063</v>
+        <v>3.318257329030797</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.033568588771935</v>
+        <v>-5.03120284684141</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.413650404598108</v>
+        <v>1.305419765980486</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2533081957918371</v>
+        <v>0.2332766272773816</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.579419181895732</v>
+        <v>3.458223305397226</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.422512117156819</v>
+        <v>3.313335181766986</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.179589275685897</v>
+        <v>-5.177223533755372</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.350319982568713</v>
+        <v>1.24208934395109</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2442251039979801</v>
+        <v>0.2241935354835247</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.569047179555608</v>
+        <v>3.447851303057101</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830332</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.584716173855863</v>
+        <v>3.47553923846603</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.271303284795483</v>
+        <v>-5.268937542864958</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.475838435623923</v>
+        <v>1.3676077970063</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2442251039979801</v>
+        <v>0.2241935354835247</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.731251236254652</v>
+        <v>3.610055359756145</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.579562811819677</v>
+        <v>3.470385876429845</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.302954943855452</v>
+        <v>-5.300589201924927</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.458024409963749</v>
+        <v>1.349793771346127</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2390566467535399</v>
+        <v>0.2190250782390845</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.722996799871801</v>
+        <v>3.601800923373295</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.589792229388169</v>
+        <v>3.480615293998336</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.384889762124335</v>
+        <v>-5.38252402019381</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.435479900224687</v>
+        <v>1.327249261607064</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2291219011664597</v>
+        <v>0.2090903326520043</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.727265370088045</v>
+        <v>3.606069493589538</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.598717867844071</v>
+        <v>3.489540932454238</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.486865884372743</v>
+        <v>-5.484500142442218</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.403615089781227</v>
+        <v>1.295384451163604</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1271457789180521</v>
+        <v>0.1071142104035967</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.675005335194903</v>
+        <v>3.553809458696397</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.590870755088246</v>
+        <v>3.481693819698414</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.376859600895521</v>
+        <v>-5.374493858964996</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.43977049041629</v>
+        <v>1.331539851798668</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1503503508353273</v>
+        <v>0.1303187823208719</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.681080965589443</v>
+        <v>3.559885089090937</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818525</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.595120765810221</v>
+        <v>3.485943830420388</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.233800025154595</v>
+        <v>-5.23143428322407</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.501244331434635</v>
+        <v>1.393013692817012</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1583637774253066</v>
+        <v>0.1383322089108512</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.690139032265405</v>
+        <v>3.568943155766899</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.602381648692757</v>
+        <v>3.493204713302924</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.932353299682758</v>
+        <v>-4.929987557752233</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.629083904505906</v>
+        <v>1.520853265888284</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.4397789343826884</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.878267950431043</v>
+        <v>3.757072073932537</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.603352826445467</v>
+        <v>3.494175891055634</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.956943543917942</v>
+        <v>-4.954577801987416</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.620218984564543</v>
+        <v>1.511988345946921</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.4397789343826884</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.879239128183754</v>
+        <v>3.758043251685248</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.604195730825223</v>
+        <v>3.49501879543539</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.905905167911421</v>
+        <v>-4.903539425980896</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.641477239346907</v>
+        <v>1.533246600729284</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.4397789343826884</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.880082032563509</v>
+        <v>3.758886156065003</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.623233829699368</v>
+        <v>3.514056894309535</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.86476587304479</v>
+        <v>-4.862400131114265</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.676971056167705</v>
+        <v>1.568740417550082</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5009497977637747</v>
+        <v>0.4809182292493193</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.923803708357633</v>
+        <v>3.802607831859127</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.439417825823303</v>
+        <v>3.33024089043347</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.76813096102615</v>
+        <v>-4.765765219095625</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.531809017099095</v>
+        <v>1.423578378481473</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5975847097824146</v>
+        <v>0.5775531412679592</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.797968651692752</v>
+        <v>3.676772775194246</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.442919869897267</v>
+        <v>3.333742934507434</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.898711695556993</v>
+        <v>-4.896345953626468</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.483078767360722</v>
+        <v>1.3748481287431</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4670039752515721</v>
+        <v>0.4469724067371167</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.723122255048211</v>
+        <v>3.601926378549704</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.427346688973349</v>
+        <v>3.318169753583517</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.734215361366031</v>
+        <v>-4.731849619435506</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.53330412011319</v>
+        <v>1.425073481495567</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.631500309442534</v>
+        <v>0.6114687409280786</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.80624687463887</v>
+        <v>3.685050998140364</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.426534399409779</v>
+        <v>3.317357464019946</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.657116759824159</v>
+        <v>-4.654751017893633</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.563331271166368</v>
+        <v>1.455100632548746</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.631500309442534</v>
+        <v>0.6114687409280786</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.8054345850753</v>
+        <v>3.684238708576794</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.436403178534852</v>
+        <v>3.327226243145019</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.667501954714048</v>
+        <v>-4.665136212783523</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.569045972335485</v>
+        <v>1.460815333717862</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6211151145526447</v>
+        <v>0.6010835460381893</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.809072247266439</v>
+        <v>3.687876370767933</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.507240184311277</v>
+        <v>3.398063248921444</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.686090113436273</v>
+        <v>-4.683724371505748</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.63244771462302</v>
+        <v>1.524217076005398</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6025269558304194</v>
+        <v>0.582495387315964</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.868756357809529</v>
+        <v>3.747560481311023</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.504109195129575</v>
+        <v>3.394932259739742</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.686388660132309</v>
+        <v>-4.684022918201784</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.629197306762904</v>
+        <v>1.520966668145282</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6022284091343835</v>
+        <v>0.582196840619928</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.865446240610205</v>
+        <v>3.7442503641117</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.508640090068967</v>
+        <v>3.399463154679134</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.585565526441881</v>
+        <v>-4.583199784511356</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.674057455178467</v>
+        <v>1.565826816560844</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6146926246187373</v>
+        <v>0.5946610561042819</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.877455664840209</v>
+        <v>3.756259788341703</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.50876934354751</v>
+        <v>3.399592408157677</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.394784165689474</v>
+        <v>-4.392418423758949</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.750499252957973</v>
+        <v>1.64226861434035</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8054739853711447</v>
+        <v>0.7854424168566893</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.992053734770197</v>
+        <v>3.870857858271691</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.488606189285107</v>
+        <v>3.379429253895274</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.287820807840053</v>
+        <v>-4.285455065909527</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.773121441835338</v>
+        <v>1.664890803217715</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8639385933309461</v>
+        <v>0.8439070248164907</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.006969345283674</v>
+        <v>3.885773468785168</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.523573125897165</v>
+        <v>3.414396190507332</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.23249021993829</v>
+        <v>-4.230124478007765</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.830220613608102</v>
+        <v>1.721989974990479</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9192691812327083</v>
+        <v>0.8992376127182529</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.07513463463679</v>
+        <v>3.953938758138284</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.517259693798603</v>
+        <v>3.40808275840877</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.220436093025327</v>
+        <v>-4.218070351094802</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.828728832274725</v>
+        <v>1.720498193657102</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9313233081456711</v>
+        <v>0.9112917396312157</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.076053678686006</v>
+        <v>3.954857802187499</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.519140323982739</v>
+        <v>3.409963388592906</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.261591212593548</v>
+        <v>-4.259225470663023</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.814147414631572</v>
+        <v>1.705916776013949</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8901681885774502</v>
+        <v>0.8701366200629947</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.053241237129209</v>
+        <v>3.932045360630703</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.531991349860621</v>
+        <v>3.422814414470788</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.193542649902018</v>
+        <v>-4.191176907971493</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.854217865586066</v>
+        <v>1.745987226968444</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.95821675126898</v>
+        <v>0.9381851827545246</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.106921400622009</v>
+        <v>3.985725524123503</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.552194020034215</v>
+        <v>3.443017084644382</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.425143043071519</v>
+        <v>-4.422777301140994</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.78178037849186</v>
+        <v>1.673549739874238</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.95821675126898</v>
+        <v>0.9381851827545246</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.127124070795603</v>
+        <v>4.005928194297097</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498973</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.535800256101097</v>
+        <v>3.426623320711264</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.475194588600738</v>
+        <v>-4.472828846670213</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.745365996347055</v>
+        <v>1.637135357729432</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.95821675126898</v>
+        <v>0.9381851827545246</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.110730306862486</v>
+        <v>3.989534430363979</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800102</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.496052169694564</v>
+        <v>3.386875234304731</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.650301421177183</v>
+        <v>-4.647935679246658</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.635575176909944</v>
+        <v>1.527344538292321</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.95821675126898</v>
+        <v>0.9381851827545246</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.070982220455952</v>
+        <v>3.949786343957446</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660854</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.503074788691504</v>
+        <v>3.393897853301671</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.619015400636727</v>
+        <v>-4.616649658706202</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.655112204123066</v>
+        <v>1.546881565505443</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9895027718094354</v>
+        <v>0.9694712032949799</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.096776451777165</v>
+        <v>3.975580575278659</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395091</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.602245788264408</v>
+        <v>3.493068852874575</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.465990008523443</v>
+        <v>-4.463624266592918</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.815493360541284</v>
+        <v>1.707262721923661</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142528163922719</v>
+        <v>1.122496595408264</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.28776268661804</v>
+        <v>4.166566810119534</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.789712013172701</v>
+        <v>3.680535077782868</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.494297322396713</v>
+        <v>-4.491931580466188</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.991636659900268</v>
+        <v>1.883406021282646</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142528163922719</v>
+        <v>1.122496595408264</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.475228911526333</v>
+        <v>4.354033035027827</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.759114964526784</v>
+        <v>3.649938029136951</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.660890547510236</v>
+        <v>-4.65852480557971</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.894402321208942</v>
+        <v>1.786171682591319</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9759349388091969</v>
+        <v>0.9559033702947415</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.344675927812302</v>
+        <v>4.223480051313796</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.762791367188501</v>
+        <v>3.653614431798669</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.63785475414867</v>
+        <v>-4.635489012218144</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.907293041215286</v>
+        <v>1.799062402597663</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9759349388091969</v>
+        <v>0.9559033702947415</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.34835233047402</v>
+        <v>4.227156453975514</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.760409422311997</v>
+        <v>3.651232486922164</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.608608773692973</v>
+        <v>-4.606243031762448</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.91660948852106</v>
+        <v>1.808378849903437</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9759349388091969</v>
+        <v>0.9559033702947415</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.345970385597515</v>
+        <v>4.224774509099009</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.757702661469632</v>
+        <v>3.648525726079799</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.715534321570824</v>
+        <v>-4.713168579640299</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.871132508527555</v>
+        <v>1.762901869909932</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8690093909313455</v>
+        <v>0.8489778224168901</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.279108296028439</v>
+        <v>4.157912419529933</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.759131463612866</v>
+        <v>3.649954528223033</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.860552880078073</v>
+        <v>-4.858187138147548</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.814553887267889</v>
+        <v>1.706323248650267</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.723990832424097</v>
+        <v>0.7039592639096416</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.193525963067325</v>
+        <v>4.072330086568818</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.859062702870619</v>
+        <v>3.749885767480786</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.97889464586279</v>
+        <v>-4.976528903932265</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.867148420211755</v>
+        <v>1.758917781594133</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7146453024725317</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.299868825462811</v>
+        <v>4.178672948964305</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.856848399996558</v>
+        <v>3.747671464606725</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.030305068183498</v>
+        <v>-5.027939326252973</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.844369948409411</v>
+        <v>1.736139309791789</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7146453024725317</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.297654522588751</v>
+        <v>4.176458646090245</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.856751528070847</v>
+        <v>3.747574592681014</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.10972451939125</v>
+        <v>-5.107358777460725</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.8125052960006</v>
+        <v>1.704274657382977</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7146453024725317</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.297557650663039</v>
+        <v>4.176361774164533</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.85674542162889</v>
+        <v>3.747568486239057</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.205187517308468</v>
+        <v>-5.202821775377942</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.774313990391756</v>
+        <v>1.666083351774133</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7146453024725317</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.297551544221083</v>
+        <v>4.176355667722577</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.854841818191501</v>
+        <v>3.745664882801668</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.140811606457753</v>
+        <v>-5.138445864527228</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.798160751294652</v>
+        <v>1.689930112677029</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.7790212133232468</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.334273487294122</v>
+        <v>4.213077610795616</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353537</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.860575635939227</v>
+        <v>3.751398700549395</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.196180768589946</v>
+        <v>-5.193815026659421</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.781746904189502</v>
+        <v>1.673516265571879</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.7790212133232468</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.340007305041849</v>
+        <v>4.218811428543343</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011328</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.86011399928216</v>
+        <v>3.750937063892327</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.241618548420774</v>
+        <v>-5.239252806490248</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.763110155600103</v>
+        <v>1.65487951698248</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.7361762226450872</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.313838673977886</v>
+        <v>4.19264279747938</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113689</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.879988392132478</v>
+        <v>3.770811456742646</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.153411714273195</v>
+        <v>-5.15104597234267</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.818267282109453</v>
+        <v>1.71003664349183</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.7361762226450872</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.333713066828205</v>
+        <v>4.212517190329698</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.863689092657206</v>
+        <v>3.754512157267373</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.047376719067886</v>
+        <v>-5.045010977137361</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.844381980716304</v>
+        <v>1.736151342098682</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.7361762226450872</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.317413767352932</v>
+        <v>4.196217890854426</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307673</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.866120042121252</v>
+        <v>3.756943106731419</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.864165055934791</v>
+        <v>-4.861799314004266</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.920097595433589</v>
+        <v>1.811866956815966</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.7361762226450872</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.319844716816978</v>
+        <v>4.198648840318472</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.831911227969142</v>
+        <v>3.722734292579309</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.79244360892094</v>
+        <v>-4.790077866990415</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.914577360087019</v>
+        <v>1.806346721469396</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8279292381733933</v>
+        <v>0.8078976696589378</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.328668770873178</v>
+        <v>4.207472894374672</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.778826973890314</v>
+        <v>3.669650038500481</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.770070583313234</v>
+        <v>-4.767704841382709</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.870442316251273</v>
+        <v>1.76221167763365</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8391849892862948</v>
+        <v>0.8191534207718394</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.282337967462091</v>
+        <v>4.161142090963585</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.964025178775669</v>
+        <v>3.854848243385836</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.803086879223978</v>
+        <v>-4.800721137293453</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.042434002772331</v>
+        <v>1.934203364154708</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7697476126195433</v>
+        <v>0.7497160441050879</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.425873746347396</v>
+        <v>4.30467786984889</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.955946404603918</v>
+        <v>3.846769469214086</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.79155924357437</v>
+        <v>-4.789193501643845</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.038966282860423</v>
+        <v>1.930735644242801</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8287482708209057</v>
+        <v>0.8087167023064503</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.453195367096462</v>
+        <v>4.331999490597957</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.959614517125707</v>
+        <v>3.850437581735874</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.888900744916739</v>
+        <v>-4.886535002986213</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.003697794845264</v>
+        <v>1.895467156227642</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7843280886554174</v>
+        <v>0.7642965201409619</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.430211370318958</v>
+        <v>4.309015493820452</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427685</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.960865599318545</v>
+        <v>3.851688663928713</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.974756774256705</v>
+        <v>-4.97239103232618</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.970606465302116</v>
+        <v>1.862375826684493</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7419520194292824</v>
+        <v>0.7219204509148269</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.406036810976115</v>
+        <v>4.284840934477609</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.943284801139047</v>
+        <v>3.834107865749215</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.983593571672825</v>
+        <v>-4.981227829742299</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.94949094815617</v>
+        <v>1.841260309538548</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7345098467879316</v>
+        <v>0.7144782782734762</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.383990709211806</v>
+        <v>4.262794832713301</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.953449312184096</v>
+        <v>3.844272376794264</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.074976134238283</v>
+        <v>-5.072610392307758</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.923102434175036</v>
+        <v>1.814871795557414</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6431272842224733</v>
+        <v>0.6230957157080179</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.339325682717581</v>
+        <v>4.218129806219076</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.055577570008364</v>
+        <v>3.946400634618533</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.063269416251277</v>
+        <v>-5.060903674320752</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.029913379194106</v>
+        <v>1.921682740576485</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6548340022094797</v>
+        <v>0.6348024336950243</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.448477971334052</v>
+        <v>4.327282094835548</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.058609908739768</v>
+        <v>3.949432973349937</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.963605912167615</v>
+        <v>-4.961240170237089</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.072811119558975</v>
+        <v>1.964580480941354</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.6979895168987108</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.489422559987668</v>
+        <v>4.368226683489164</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.271514742017827</v>
+        <v>4.162337806627995</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.973922010333967</v>
+        <v>-4.971556268403441</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.281589513570493</v>
+        <v>2.173358874952871</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.6979895168987108</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.702327393265726</v>
+        <v>4.581131516767222</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.270693408929916</v>
+        <v>4.161516473540085</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.973828042316594</v>
+        <v>-4.971462300386069</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.280805767689531</v>
+        <v>2.172575129071911</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.7183909467604842</v>
+        <v>0.6983593782460288</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.701727976986207</v>
+        <v>4.580532100487702</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.26492539487427</v>
+        <v>4.155748459484439</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.981046866516438</v>
+        <v>-4.978681124585913</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.272150223953948</v>
+        <v>2.163919585336326</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.7183909467604842</v>
+        <v>0.6983593782460288</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.69595996293056</v>
+        <v>4.574764086432056</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740925</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.26492539487427</v>
+        <v>4.155748459484439</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.9800984433984</v>
+        <v>-5.193817606436922</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.272529593201163</v>
+        <v>2.077864992595923</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.7183909467604842</v>
+        <v>0.6983593782460288</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.69595996293056</v>
+        <v>4.574764086432056</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.887298152656555</v>
+        <v>3.584905156194611</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.359411497323526</v>
+        <v>4.168476067465531</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.158006192402877</v>
+        <v>-5.152308470044808</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.295852596048628</v>
+        <v>2.10719625513386</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.7183909467604842</v>
+        <v>0.6894776896547269</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.790446065379816</v>
+        <v>4.582162681258367</v>
       </c>
     </row>
   </sheetData>
